--- a/MonkeyType/Examen_clavier.xlsx
+++ b/MonkeyType/Examen_clavier.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cshawi-my.sharepoint.com/personal/mcbelanger_cshawi_ca/Documents/_Cegep_info/Ses_Automne/0Q4_Initiation à la profession/evaluations/clavier/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cegep\420-0Q4-SW-Initiation-profession\MonkeyType\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{B2FCD3C6-6290-48C8-B1C0-CA5B29976174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{945475D6-991D-42F1-8CA4-773DBB42D8AE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92951FCC-D1E2-40C6-B79B-F3A2E15A907C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-10230" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BFE994-FE53-4B35-81E8-8EC2FCAE1962}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F4BFE994-FE53-4B35-81E8-8EC2FCAE1962}"/>
   </bookViews>
   <sheets>
     <sheet name="horaire examen clavier" sheetId="1" r:id="rId1"/>
@@ -41,21 +41,12 @@
     <t>Examen Excel</t>
   </si>
   <si>
-    <t>14h30</t>
-  </si>
-  <si>
-    <t>15h30</t>
-  </si>
-  <si>
     <t>14h50</t>
   </si>
   <si>
     <t>15h10</t>
   </si>
   <si>
-    <t>15h50</t>
-  </si>
-  <si>
     <t>nom 1</t>
   </si>
   <si>
@@ -168,6 +159,15 @@
   </si>
   <si>
     <t>69 et -</t>
+  </si>
+  <si>
+    <t>13h30</t>
+  </si>
+  <si>
+    <t>13h50</t>
+  </si>
+  <si>
+    <t>14h10</t>
   </si>
 </sst>
 </file>
@@ -244,14 +244,14 @@
     <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -268,10 +268,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,222 +607,222 @@
         <v>45989</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="A8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="B15" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B16" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="B17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="B18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="7">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B23" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="B24" s="6">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
         <v>-3</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="wkiAWVFuRsHwDpGsrJQqZH5g9fiNF6a/y4IN44Zk+n3RRz4mbxYiM+VfLWcVHbZQRNBZUen2z9qOUWU3VjJd0A==" saltValue="QXvtJONLN41s2w7P55irRg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4rgUSvX7HNa9+ARfYCkRKdeP/RbBhCFtVeBccpOp38MDKAUArvAouV65PuFpFPXg5EzgTly8eJyVPB6/Ux3NPQ==" saltValue="M33P1YEaaTOnL75NlT6iSw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="D2:F6" name="Plage1"/>
   </protectedRanges>
